--- a/data/dim_lojas.xlsx
+++ b/data/dim_lojas.xlsx
@@ -567,10 +567,10 @@
         </is>
       </c>
       <c r="L2" s="1" t="n">
-        <v>42171</v>
+        <v>42557</v>
       </c>
       <c r="M2" t="n">
-        <v>246</v>
+        <v>107</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -578,13 +578,13 @@
         </is>
       </c>
       <c r="O2" t="n">
-        <v>130</v>
+        <v>2</v>
       </c>
       <c r="P2" t="n">
-        <v>-1.783396</v>
+        <v>-6.818375</v>
       </c>
       <c r="Q2" t="n">
-        <v>-48.077746</v>
+        <v>-41.399915</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
@@ -647,10 +647,10 @@
         </is>
       </c>
       <c r="L3" s="1" t="n">
-        <v>41729</v>
+        <v>43880</v>
       </c>
       <c r="M3" t="n">
-        <v>118</v>
+        <v>167</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -658,13 +658,13 @@
         </is>
       </c>
       <c r="O3" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="P3" t="n">
-        <v>-2.669915</v>
+        <v>-23.670837</v>
       </c>
       <c r="Q3" t="n">
-        <v>-50.204508</v>
+        <v>-71.348651</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
@@ -727,10 +727,10 @@
         </is>
       </c>
       <c r="L4" s="1" t="n">
-        <v>42584</v>
+        <v>45465</v>
       </c>
       <c r="M4" t="n">
-        <v>254</v>
+        <v>199</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -738,13 +738,13 @@
         </is>
       </c>
       <c r="O4" t="n">
-        <v>37</v>
+        <v>140</v>
       </c>
       <c r="P4" t="n">
-        <v>-10.080094</v>
+        <v>-15.959757</v>
       </c>
       <c r="Q4" t="n">
-        <v>-69.936245</v>
+        <v>-35.998969</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="L5" s="1" t="n">
-        <v>43250</v>
+        <v>45145</v>
       </c>
       <c r="M5" t="n">
-        <v>224</v>
+        <v>172</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
@@ -818,13 +818,13 @@
         </is>
       </c>
       <c r="O5" t="n">
-        <v>85</v>
+        <v>13</v>
       </c>
       <c r="P5" t="n">
-        <v>-27.057838</v>
+        <v>-8.752744</v>
       </c>
       <c r="Q5" t="n">
-        <v>-49.830772</v>
+        <v>-72.02631700000001</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
@@ -887,10 +887,10 @@
         </is>
       </c>
       <c r="L6" s="1" t="n">
-        <v>44347</v>
+        <v>44770</v>
       </c>
       <c r="M6" t="n">
-        <v>32</v>
+        <v>67</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
@@ -898,13 +898,13 @@
         </is>
       </c>
       <c r="O6" t="n">
-        <v>78</v>
+        <v>135</v>
       </c>
       <c r="P6" t="n">
-        <v>-27.937644</v>
+        <v>-15.939051</v>
       </c>
       <c r="Q6" t="n">
-        <v>-63.999008</v>
+        <v>-55.259975</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
@@ -967,10 +967,10 @@
         </is>
       </c>
       <c r="L7" s="1" t="n">
-        <v>45432</v>
+        <v>42171</v>
       </c>
       <c r="M7" t="n">
-        <v>152</v>
+        <v>246</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -978,13 +978,13 @@
         </is>
       </c>
       <c r="O7" t="n">
-        <v>43</v>
+        <v>60</v>
       </c>
       <c r="P7" t="n">
-        <v>-10.894251</v>
+        <v>-1.783396</v>
       </c>
       <c r="Q7" t="n">
-        <v>-63.394845</v>
+        <v>-48.077746</v>
       </c>
       <c r="R7" t="inlineStr">
         <is>
@@ -1047,10 +1047,10 @@
         </is>
       </c>
       <c r="L8" s="1" t="n">
-        <v>42581</v>
+        <v>41729</v>
       </c>
       <c r="M8" t="n">
-        <v>86</v>
+        <v>118</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
@@ -1058,13 +1058,13 @@
         </is>
       </c>
       <c r="O8" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="P8" t="n">
-        <v>-11.499931</v>
+        <v>-2.669915</v>
       </c>
       <c r="Q8" t="n">
-        <v>-53.438548</v>
+        <v>-50.204508</v>
       </c>
       <c r="R8" t="inlineStr">
         <is>
@@ -1127,10 +1127,10 @@
         </is>
       </c>
       <c r="L9" s="1" t="n">
-        <v>42594</v>
+        <v>42584</v>
       </c>
       <c r="M9" t="n">
-        <v>263</v>
+        <v>254</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
@@ -1138,13 +1138,13 @@
         </is>
       </c>
       <c r="O9" t="n">
-        <v>36</v>
+        <v>105</v>
       </c>
       <c r="P9" t="n">
-        <v>-8.812932999999999</v>
+        <v>-10.080094</v>
       </c>
       <c r="Q9" t="n">
-        <v>-58.357797</v>
+        <v>-69.936245</v>
       </c>
       <c r="R9" t="inlineStr">
         <is>
@@ -1207,10 +1207,10 @@
         </is>
       </c>
       <c r="L10" s="1" t="n">
-        <v>44926</v>
+        <v>43250</v>
       </c>
       <c r="M10" t="n">
-        <v>112</v>
+        <v>224</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
@@ -1218,13 +1218,13 @@
         </is>
       </c>
       <c r="O10" t="n">
-        <v>123</v>
+        <v>17</v>
       </c>
       <c r="P10" t="n">
-        <v>-2.577918</v>
+        <v>-27.057838</v>
       </c>
       <c r="Q10" t="n">
-        <v>-68.116398</v>
+        <v>-49.830772</v>
       </c>
       <c r="R10" t="inlineStr">
         <is>
@@ -1287,10 +1287,10 @@
         </is>
       </c>
       <c r="L11" s="1" t="n">
-        <v>41818</v>
+        <v>44347</v>
       </c>
       <c r="M11" t="n">
-        <v>236</v>
+        <v>32</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
@@ -1298,13 +1298,13 @@
         </is>
       </c>
       <c r="O11" t="n">
-        <v>141</v>
+        <v>81</v>
       </c>
       <c r="P11" t="n">
-        <v>-23.296963</v>
+        <v>-27.937644</v>
       </c>
       <c r="Q11" t="n">
-        <v>-46.042739</v>
+        <v>-63.999008</v>
       </c>
       <c r="R11" t="inlineStr">
         <is>
@@ -1367,10 +1367,10 @@
         </is>
       </c>
       <c r="L12" s="1" t="n">
-        <v>44934</v>
+        <v>45432</v>
       </c>
       <c r="M12" t="n">
-        <v>143</v>
+        <v>152</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
@@ -1378,13 +1378,13 @@
         </is>
       </c>
       <c r="O12" t="n">
-        <v>142</v>
+        <v>4</v>
       </c>
       <c r="P12" t="n">
-        <v>-10.811261</v>
+        <v>-10.894251</v>
       </c>
       <c r="Q12" t="n">
-        <v>-36.309841</v>
+        <v>-63.394845</v>
       </c>
       <c r="R12" t="inlineStr">
         <is>
@@ -1447,10 +1447,10 @@
         </is>
       </c>
       <c r="L13" s="1" t="n">
-        <v>42524</v>
+        <v>42581</v>
       </c>
       <c r="M13" t="n">
-        <v>246</v>
+        <v>86</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
@@ -1458,13 +1458,13 @@
         </is>
       </c>
       <c r="O13" t="n">
-        <v>135</v>
+        <v>28</v>
       </c>
       <c r="P13" t="n">
-        <v>-26.033955</v>
+        <v>-11.499931</v>
       </c>
       <c r="Q13" t="n">
-        <v>-59.447224</v>
+        <v>-53.438548</v>
       </c>
       <c r="R13" t="inlineStr">
         <is>
@@ -1527,10 +1527,10 @@
         </is>
       </c>
       <c r="L14" s="1" t="n">
-        <v>42972</v>
+        <v>42594</v>
       </c>
       <c r="M14" t="n">
-        <v>143</v>
+        <v>263</v>
       </c>
       <c r="N14" t="inlineStr">
         <is>
@@ -1538,13 +1538,13 @@
         </is>
       </c>
       <c r="O14" t="n">
-        <v>108</v>
+        <v>33</v>
       </c>
       <c r="P14" t="n">
-        <v>-17.725191</v>
+        <v>-8.812932999999999</v>
       </c>
       <c r="Q14" t="n">
-        <v>-46.896964</v>
+        <v>-58.357797</v>
       </c>
       <c r="R14" t="inlineStr">
         <is>
@@ -1607,10 +1607,10 @@
         </is>
       </c>
       <c r="L15" s="1" t="n">
-        <v>44497</v>
+        <v>44926</v>
       </c>
       <c r="M15" t="n">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="N15" t="inlineStr">
         <is>
@@ -1618,13 +1618,13 @@
         </is>
       </c>
       <c r="O15" t="n">
-        <v>137</v>
+        <v>86</v>
       </c>
       <c r="P15" t="n">
-        <v>-20.512405</v>
+        <v>-2.577918</v>
       </c>
       <c r="Q15" t="n">
-        <v>-51.476792</v>
+        <v>-68.116398</v>
       </c>
       <c r="R15" t="inlineStr">
         <is>
@@ -1687,10 +1687,10 @@
         </is>
       </c>
       <c r="L16" s="1" t="n">
-        <v>44809</v>
+        <v>41818</v>
       </c>
       <c r="M16" t="n">
-        <v>202</v>
+        <v>236</v>
       </c>
       <c r="N16" t="inlineStr">
         <is>
@@ -1698,13 +1698,13 @@
         </is>
       </c>
       <c r="O16" t="n">
-        <v>71</v>
+        <v>95</v>
       </c>
       <c r="P16" t="n">
-        <v>-17.09724</v>
+        <v>-23.296963</v>
       </c>
       <c r="Q16" t="n">
-        <v>-66.443393</v>
+        <v>-46.042739</v>
       </c>
       <c r="R16" t="inlineStr">
         <is>
